--- a/outputs/49857.xlsx
+++ b/outputs/49857.xlsx
@@ -635,7 +635,7 @@
         <v>12</v>
       </c>
       <c r="G4" s="4" t="n">
-        <f aca="false">IF(F4="YES",COUNTIF($F$4:F4,"YES"),0)</f>
+        <f aca="false">IF(F4="Yes",COUNTIF($F$4:F4,"Yes"),0)</f>
         <v>1</v>
       </c>
       <c r="H4" s="8" t="n">
@@ -663,7 +663,7 @@
         <v>15</v>
       </c>
       <c r="G5" s="4" t="n">
-        <f aca="false">IF(F5="YES",COUNTIF($F$4:F5,"YES"),0)</f>
+        <f aca="false">IF(F5="Yes",COUNTIF($F$4:F5,"Yes"),0)</f>
         <v>0</v>
       </c>
       <c r="H5" s="8" t="n">
@@ -691,7 +691,7 @@
         <v>15</v>
       </c>
       <c r="G6" s="4" t="n">
-        <f aca="false">IF(F6="YES",COUNTIF($F$4:F6,"YES"),0)</f>
+        <f aca="false">IF(F6="Yes",COUNTIF($F$4:F6,"Yes"),0)</f>
         <v>0</v>
       </c>
       <c r="H6" s="8" t="n">
@@ -719,7 +719,7 @@
         <v>12</v>
       </c>
       <c r="G7" s="4" t="n">
-        <f aca="false">IF(F7="YES",COUNTIF($F$4:F7,"YES"),0)</f>
+        <f aca="false">IF(F7="Yes",COUNTIF($F$4:F7,"Yes"),0)</f>
         <v>2</v>
       </c>
       <c r="H7" s="8" t="n">
@@ -747,7 +747,7 @@
         <v>12</v>
       </c>
       <c r="G8" s="4" t="n">
-        <f aca="false">IF(F8="YES",COUNTIF($F$4:F8,"YES"),0)</f>
+        <f aca="false">IF(F8="Yes",COUNTIF($F$4:F8,"Yes"),0)</f>
         <v>3</v>
       </c>
       <c r="H8" s="8" t="n">
@@ -775,7 +775,7 @@
         <v>15</v>
       </c>
       <c r="G9" s="4" t="n">
-        <f aca="false">IF(F9="YES",COUNTIF($F$4:F9,"YES"),0)</f>
+        <f aca="false">IF(F9="Yes",COUNTIF($F$4:F9,"Yes"),0)</f>
         <v>0</v>
       </c>
       <c r="H9" s="8" t="n">
@@ -803,7 +803,7 @@
         <v>12</v>
       </c>
       <c r="G10" s="4" t="n">
-        <f aca="false">IF(F10="YES",COUNTIF($F$4:F10,"YES"),0)</f>
+        <f aca="false">IF(F10="Yes",COUNTIF($F$4:F10,"Yes"),0)</f>
         <v>4</v>
       </c>
       <c r="H10" s="8" t="n">

--- a/outputs/49857.xlsx
+++ b/outputs/49857.xlsx
@@ -635,7 +635,7 @@
         <v>12</v>
       </c>
       <c r="G4" s="4" t="n">
-        <f aca="false">IF(F4="Yes",COUNTIF($F$4:F4,"Yes"),0)</f>
+        <f aca="false">IF(F4="Yes",1,0)</f>
         <v>1</v>
       </c>
       <c r="H4" s="8" t="n">
@@ -663,7 +663,7 @@
         <v>15</v>
       </c>
       <c r="G5" s="4" t="n">
-        <f aca="false">IF(F5="Yes",COUNTIF($F$4:F5,"Yes"),0)</f>
+        <f aca="false">IF(F5="Yes",G4+1,0)</f>
         <v>0</v>
       </c>
       <c r="H5" s="8" t="n">
@@ -691,7 +691,7 @@
         <v>15</v>
       </c>
       <c r="G6" s="4" t="n">
-        <f aca="false">IF(F6="Yes",COUNTIF($F$4:F6,"Yes"),0)</f>
+        <f aca="false">IF(F6="Yes",G5+1,0)</f>
         <v>0</v>
       </c>
       <c r="H6" s="8" t="n">
@@ -719,8 +719,8 @@
         <v>12</v>
       </c>
       <c r="G7" s="4" t="n">
-        <f aca="false">IF(F7="Yes",COUNTIF($F$4:F7,"Yes"),0)</f>
-        <v>2</v>
+        <f aca="false">IF(F7="Yes",G6+1,0)</f>
+        <v>1</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>9250</v>
@@ -747,8 +747,8 @@
         <v>12</v>
       </c>
       <c r="G8" s="4" t="n">
-        <f aca="false">IF(F8="Yes",COUNTIF($F$4:F8,"Yes"),0)</f>
-        <v>3</v>
+        <f aca="false">IF(F8="Yes",G7+1,0)</f>
+        <v>2</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>3500</v>
@@ -775,7 +775,7 @@
         <v>15</v>
       </c>
       <c r="G9" s="4" t="n">
-        <f aca="false">IF(F9="Yes",COUNTIF($F$4:F9,"Yes"),0)</f>
+        <f aca="false">IF(F9="Yes",G8+1,0)</f>
         <v>0</v>
       </c>
       <c r="H9" s="8" t="n">
@@ -803,8 +803,8 @@
         <v>12</v>
       </c>
       <c r="G10" s="4" t="n">
-        <f aca="false">IF(F10="Yes",COUNTIF($F$4:F10,"Yes"),0)</f>
-        <v>4</v>
+        <f aca="false">IF(F10="Yes",G9+1,0)</f>
+        <v>1</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>7320</v>
